--- a/artfynd/A 40942-2023 artfynd.xlsx
+++ b/artfynd/A 40942-2023 artfynd.xlsx
@@ -3413,7 +3413,7 @@
         <v>113313681</v>
       </c>
       <c r="B25" t="n">
-        <v>55976</v>
+        <v>55977</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 40942-2023 artfynd.xlsx
+++ b/artfynd/A 40942-2023 artfynd.xlsx
@@ -3413,7 +3413,7 @@
         <v>113313681</v>
       </c>
       <c r="B25" t="n">
-        <v>55977</v>
+        <v>55980</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 40942-2023 artfynd.xlsx
+++ b/artfynd/A 40942-2023 artfynd.xlsx
@@ -3413,7 +3413,7 @@
         <v>113313681</v>
       </c>
       <c r="B25" t="n">
-        <v>55980</v>
+        <v>55984</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 40942-2023 artfynd.xlsx
+++ b/artfynd/A 40942-2023 artfynd.xlsx
@@ -3413,7 +3413,7 @@
         <v>113313681</v>
       </c>
       <c r="B25" t="n">
-        <v>55984</v>
+        <v>55991</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 40942-2023 artfynd.xlsx
+++ b/artfynd/A 40942-2023 artfynd.xlsx
@@ -3413,7 +3413,7 @@
         <v>113313681</v>
       </c>
       <c r="B25" t="n">
-        <v>55991</v>
+        <v>55993</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 40942-2023 artfynd.xlsx
+++ b/artfynd/A 40942-2023 artfynd.xlsx
@@ -3413,7 +3413,7 @@
         <v>113313681</v>
       </c>
       <c r="B25" t="n">
-        <v>55993</v>
+        <v>56021</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 40942-2023 artfynd.xlsx
+++ b/artfynd/A 40942-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40942-2023 artfynd.xlsx
+++ b/artfynd/A 40942-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73445077</v>
+        <v>97069965</v>
       </c>
       <c r="B2" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>373</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grentaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacodon septentrionalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandtorpsskogen, Ramnäs sn, Vstm</t>
+          <t>Sandtorp, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559903.1517287814</v>
+        <v>560235</v>
       </c>
       <c r="R2" t="n">
-        <v>6629833.193362198</v>
+        <v>6630000</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-10-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I de gamla lönnarna</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,62 +774,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Solveig Hagfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73445041</v>
+        <v>220695</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>698</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandtorpsskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Sandtorp, 8 km V väg 66 i jämnhöjd St Nadden, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560093.2930822695</v>
+        <v>560222</v>
       </c>
       <c r="R3" t="n">
-        <v>6629734.596450471</v>
+        <v>6629990</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-10-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2003-08-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2003-08-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,74 +860,82 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Lieslåtter sen 1994</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73445064</v>
+        <v>111998105</v>
       </c>
       <c r="B4" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5448</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Sandtorp, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560102.5606225387</v>
+        <v>560212</v>
       </c>
       <c r="R4" t="n">
-        <v>6629722.667087294</v>
+        <v>6629616</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-10-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-10-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,76 +980,63 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Seppo Ormiskangas, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69576415</v>
+        <v>112450679</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ulvramenskogen, Kvarnbäcken, Ramnäs sn, Vstm</t>
+          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560301.4990031295</v>
+        <v>560109</v>
       </c>
       <c r="R5" t="n">
-        <v>6629517.516098694</v>
+        <v>6629780</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,22 +1060,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-02-18</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-02-18</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,79 +1084,69 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>76893402</v>
+        <v>73445064</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandtorpsskogen, Ramnäs,Vstm, Vstm</t>
+          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559907.1513793083</v>
+        <v>560103</v>
       </c>
       <c r="R6" t="n">
-        <v>6629835.27090948</v>
+        <v>6629723</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,27 +1170,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-04-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-04-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flertal blommande plantor på vacker öppen glänta med inslag av lövträd, död ved.</t>
+          <t>2018-10-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,15 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104996756</v>
+        <v>73445041</v>
       </c>
       <c r="B7" t="n">
-        <v>57193</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,53 +1214,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
+          <t>Sandtorpsskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560246.3244882654</v>
+        <v>560093</v>
       </c>
       <c r="R7" t="n">
-        <v>6630028.972379012</v>
+        <v>6629735</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,22 +1270,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-12-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2018-10-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-12-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2018-10-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,6 +1284,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1397,22 +1296,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Solveig Hagfors</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111840447</v>
+        <v>112455745</v>
       </c>
       <c r="B8" t="n">
-        <v>56575</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,53 +1314,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
+          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560221</v>
+        <v>560085</v>
       </c>
       <c r="R8" t="n">
-        <v>6629993</v>
+        <v>6629821</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1490,22 +1371,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,8 +1385,14 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1532,15 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111998059</v>
+        <v>69576415</v>
       </c>
       <c r="B9" t="n">
-        <v>96656</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,41 +1420,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandtorp, Ramnäs sn, Vstm</t>
+          <t>Ulvramenskogen, Kvarnbäcken, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560170</v>
+        <v>560301</v>
       </c>
       <c r="R9" t="n">
-        <v>6629712</v>
+        <v>6629518</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1606,17 +1485,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2018-02-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Enstaka plantor</t>
+          <t>2018-02-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,7 +1509,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1637,22 +1520,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sören Larsson, Seppo Ormiskangas, Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111998105</v>
+        <v>90448136</v>
       </c>
       <c r="B10" t="n">
-        <v>90811</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,48 +1538,57 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4363</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandtorp, Ramnäs sn, Vstm</t>
+          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560212</v>
+        <v>560188</v>
       </c>
       <c r="R10" t="n">
-        <v>6629616</v>
+        <v>6629845</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1725,12 +1612,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2021-01-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2021-01-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,34 +1636,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sören Larsson, Seppo Ormiskangas, Pia Hagfors</t>
+          <t>Solveig Hagfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111998125</v>
+        <v>90747812</v>
       </c>
       <c r="B11" t="n">
-        <v>57610</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,31 +1665,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208250</v>
+        <v>100110</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1809,23 +1695,27 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandtorp, Ramnäs sn, Vstm</t>
+          <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560212</v>
+        <v>560237</v>
       </c>
       <c r="R11" t="n">
-        <v>6629599</v>
+        <v>6629980</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1849,12 +1739,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2021-02-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2021-02-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Vid fågelmatning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,84 +1768,87 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sören Larsson, Seppo Ormiskangas, Pia Hagfors</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111973132</v>
+        <v>122573658</v>
       </c>
       <c r="B12" t="n">
-        <v>56575</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560246</v>
+        <v>560155</v>
       </c>
       <c r="R12" t="n">
-        <v>6630029</v>
+        <v>6629917</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1964,22 +1872,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2009-06-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2009-06-13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>En salamander sågs vilande vid dammkanten, två simmandes i dammen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,8 +1901,14 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1999,69 +1918,72 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Pia Hagfors, Solveig Hagfors</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111998133</v>
+        <v>113313681</v>
       </c>
       <c r="B13" t="n">
-        <v>56575</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sandtorp, Ramnäs sn, Vstm</t>
+          <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560223</v>
+        <v>560221</v>
       </c>
       <c r="R13" t="n">
-        <v>6629558</v>
+        <v>6629993</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2088,12 +2010,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-11-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-11-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Var på marken invid fågelmatningen. Skrämde dem och de flög in mot den täta granskogen N om matningen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,59 +2045,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sören Larsson, Seppo Ormiskangas, Pia Hagfors</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112452606</v>
+        <v>122899318</v>
       </c>
       <c r="B14" t="n">
-        <v>107661</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2168,14 +2108,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Sandtorpsskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559904</v>
+        <v>560171</v>
       </c>
       <c r="R14" t="n">
-        <v>6629871</v>
+        <v>6629923</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2202,12 +2142,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Järpen uppskrämd, flög i riktning S, mot hästboxarna.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2216,9 +2171,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2228,22 +2187,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Solveig Hagfors</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112454580</v>
+        <v>92181273</v>
       </c>
       <c r="B15" t="n">
-        <v>99098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,31 +2205,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>102977</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2283,14 +2245,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559890</v>
+        <v>560221</v>
       </c>
       <c r="R15" t="n">
-        <v>6629844</v>
+        <v>6629993</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2317,12 +2279,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2021-04-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2021-04-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På myrstack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,7 +2308,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2343,22 +2319,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Solveig Hagfors</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112452947</v>
+        <v>92376404</v>
       </c>
       <c r="B16" t="n">
-        <v>107661</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2366,31 +2337,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>102987</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2398,14 +2377,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559899</v>
+        <v>560237</v>
       </c>
       <c r="R16" t="n">
-        <v>6629860</v>
+        <v>6629980</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2432,12 +2411,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Vid fågelmatning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2446,7 +2440,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2458,54 +2451,57 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Solveig Hagfors</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112455017</v>
+        <v>99911911</v>
       </c>
       <c r="B17" t="n">
-        <v>99098</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>102987</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2513,14 +2509,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559943</v>
+        <v>560183</v>
       </c>
       <c r="R17" t="n">
-        <v>6629847</v>
+        <v>6629892</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2547,12 +2543,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2022-04-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2022-04-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,7 +2567,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2573,60 +2578,68 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Solveig Hagfors</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112450679</v>
+        <v>111840447</v>
       </c>
       <c r="B18" t="n">
-        <v>90910</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4363</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560109</v>
+        <v>560221</v>
       </c>
       <c r="R18" t="n">
-        <v>6629780</v>
+        <v>6629993</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2653,22 +2666,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2677,7 +2690,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2696,62 +2708,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112452571</v>
+        <v>111973132</v>
       </c>
       <c r="B19" t="n">
-        <v>99098</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559904</v>
+        <v>560246</v>
       </c>
       <c r="R19" t="n">
-        <v>6629871</v>
+        <v>6630029</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2778,12 +2785,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2792,7 +2809,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2811,61 +2827,60 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112636645</v>
+        <v>111998133</v>
       </c>
       <c r="B20" t="n">
-        <v>99249</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sandtorp V, Vstm</t>
+          <t>Sandtorp, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559947</v>
+        <v>560223</v>
       </c>
       <c r="R20" t="n">
-        <v>6629877</v>
+        <v>6629558</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2889,12 +2904,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,82 +2918,75 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tom Sävström, Pia Hagfors</t>
+          <t>Sören Larsson, Seppo Ormiskangas, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112636749</v>
+        <v>112880970</v>
       </c>
       <c r="B21" t="n">
-        <v>100145</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sandtorp V, Vstm</t>
+          <t>Sandtorpskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559914</v>
+        <v>560241</v>
       </c>
       <c r="R21" t="n">
-        <v>6629825</v>
+        <v>6630060</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3005,12 +3013,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3019,86 +3037,78 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tom Sävström, Pia Hagfors</t>
+          <t>Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112636794</v>
+        <v>112881194</v>
       </c>
       <c r="B22" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandtorp V, Vstm</t>
+          <t>Sandtorpsskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559918</v>
+        <v>560132</v>
       </c>
       <c r="R22" t="n">
-        <v>6629825</v>
+        <v>6629772</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3122,12 +3132,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3136,44 +3156,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tom Sävström, Pia Hagfors</t>
+          <t>Sören Larsson, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112881120</v>
+        <v>73445077</v>
       </c>
       <c r="B23" t="n">
-        <v>99424</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3181,31 +3185,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3213,13 +3218,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559962</v>
+        <v>559903</v>
       </c>
       <c r="R23" t="n">
-        <v>6629880</v>
+        <v>6629833</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3243,22 +3248,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2018-10-07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2018-10-07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3274,77 +3269,73 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sören Larsson, Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112881194</v>
+        <v>112453543</v>
       </c>
       <c r="B24" t="n">
-        <v>56901</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sandtorpsskogen, Ramnäs sn, Vstm</t>
+          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560132</v>
+        <v>559856</v>
       </c>
       <c r="R24" t="n">
-        <v>6629772</v>
+        <v>6629840</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3368,22 +3359,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3392,91 +3373,76 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sören Larsson, Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113313681</v>
+        <v>112636794</v>
       </c>
       <c r="B25" t="n">
-        <v>56470</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
+          <t>Sandtorp V, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560221</v>
+        <v>559918</v>
       </c>
       <c r="R25" t="n">
-        <v>6629993</v>
+        <v>6629825</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3500,27 +3466,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Var på marken invid fågelmatningen. Skrämde dem och de flög in mot den täta granskogen N om matningen.</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3529,21 +3480,1884 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>110568138</v>
+      </c>
+      <c r="B26" t="n">
+        <v>43219</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>201028</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Thymelicus lineola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>560183</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6629892</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Solveig Hagfors</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>110499151</v>
+      </c>
+      <c r="B27" t="n">
+        <v>43454</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>201108</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Starrgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Coenonympha tullia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Müller, 1764)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>560183</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6629892</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
         <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Solveig Hagfors</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>104996756</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sandtorp, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>560246</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6630029</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-12-09</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-12-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Solveig Hagfors</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>111997906</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sandtorp, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>560053</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6629970</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Seppo Ormiskangas, Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>111998125</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sandtorp, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>560212</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6629599</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Seppo Ormiskangas, Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>112452234</v>
+      </c>
+      <c r="B31" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>559899</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6629860</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Öppen skogsdunge med blandskog av löv, tall och gran.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>112452606</v>
+      </c>
+      <c r="B32" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>559904</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6629871</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>112636749</v>
+      </c>
+      <c r="B33" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sandtorp V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>559914</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6629825</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>76893402</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sandtorpsskogen, Ramnäs,Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>559907</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6629835</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2019-04-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2019-04-07</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Flertal blommande plantor på vacker öppen glänta med inslag av lövträd, död ved.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>112452571</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>559904</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6629871</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>112454580</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>559890</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6629844</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>112455017</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sandtorpsskogen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>559943</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6629847</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>112636645</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sandtorp V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>559947</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6629877</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>112881120</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sandtorpsskogen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>559962</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6629880</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>112881152</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sandtorpsskogen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>559944</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6629786</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spridda plantor</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>111998059</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sandtorp, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>560170</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6629712</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Enstaka plantor</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Seppo Ormiskangas, Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40942-2023 artfynd.xlsx
+++ b/artfynd/A 40942-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97069965</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/220695</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111998105</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112450679</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73445064</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73445041</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112455745</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69576415</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,6 +1696,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90448136</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1783,6 +1833,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90747812</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1922,6 +1977,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122573658</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2054,6 +2114,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113313681</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2191,6 +2256,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122899318</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2323,6 +2393,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92181273</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2455,6 +2530,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92376404</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2582,6 +2662,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99911911</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2705,6 +2790,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840447</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2824,6 +2914,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111973132</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2933,6 +3028,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111998133</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3052,6 +3152,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112880970</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3171,6 +3276,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112881194</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3278,6 +3388,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73445077</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3389,6 +3504,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112453543</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3506,6 +3626,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112636794</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3635,6 +3760,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110568138</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3764,6 +3894,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110499151</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3887,6 +4022,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104996756</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4002,6 +4142,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111997906</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4121,6 +4266,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111998125</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4241,6 +4391,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112452234</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4351,6 +4506,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112452606</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4462,6 +4622,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112636749</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4573,6 +4738,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76893402</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4683,6 +4853,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112452571</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4793,6 +4968,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112454580</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4903,6 +5083,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112455017</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5014,6 +5199,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112636645</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5130,6 +5320,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112881120</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5251,6 +5446,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112881152</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5358,8 +5558,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111998059</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>